--- a/artfynd/S 6380-2022 artfynd.xlsx
+++ b/artfynd/S 6380-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,48 +1457,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55544986</v>
+        <v>137373651</v>
       </c>
       <c r="B9" t="n">
-        <v>96437</v>
+        <v>90896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>1594</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Tricholoma atrosquamosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Eklund, SV om, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696788</v>
+        <v>697076</v>
       </c>
       <c r="R9" t="n">
-        <v>6643613</v>
+        <v>6643865</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,17 +1531,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal asp.</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,24 +1561,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55544986</t>
+          <t>https://artportalen.se/Sighting/137373651</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55545596</v>
+        <v>55544986</v>
       </c>
       <c r="B10" t="n">
         <v>96437</v>
@@ -1601,14 +1612,14 @@
       <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Eklund, SV om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697019</v>
+        <v>696788</v>
       </c>
       <c r="R10" t="n">
-        <v>6643848</v>
+        <v>6643613</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1645,7 +1656,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På block och gammal asp. Gammal barrblandskog på delvis kalkhaltig mark.</t>
+          <t>På gammal asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,16 +1682,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545596</t>
+          <t>https://artportalen.se/Sighting/55544986</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55544996</v>
+        <v>55545596</v>
       </c>
       <c r="B11" t="n">
-        <v>91893</v>
+        <v>96437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,36 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eklund, SV om, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696803</v>
+        <v>697019</v>
       </c>
       <c r="R11" t="n">
-        <v>6643628</v>
+        <v>6643848</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1754,7 +1766,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På asphögstubbe.</t>
+          <t>På block och gammal asp. Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1775,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1781,16 +1792,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55544996</t>
+          <t>https://artportalen.se/Sighting/55545596</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>55544974</v>
+        <v>55544996</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>91893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,21 +1809,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>4660</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1824,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696765</v>
+        <v>696803</v>
       </c>
       <c r="R12" t="n">
-        <v>6643599</v>
+        <v>6643628</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1862,6 +1873,11 @@
           <t>2015-10-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På asphögstubbe.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1886,38 +1902,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55544974</t>
+          <t>https://artportalen.se/Sighting/55544996</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>55545508</v>
+        <v>55544974</v>
       </c>
       <c r="B13" t="n">
-        <v>91930</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,14 +1941,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Eklund, SV om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697118</v>
+        <v>696765</v>
       </c>
       <c r="R13" t="n">
-        <v>6643936</v>
+        <v>6643599</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1967,11 +1983,6 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1996,16 +2007,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545508</t>
+          <t>https://artportalen.se/Sighting/55544974</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55545129</v>
+        <v>55545508</v>
       </c>
       <c r="B14" t="n">
-        <v>93233</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2035,14 +2046,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Eklund, SV om, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696785</v>
+        <v>697118</v>
       </c>
       <c r="R14" t="n">
-        <v>6643600</v>
+        <v>6643936</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,6 +2088,11 @@
           <t>2015-10-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2101,13 +2117,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545129</t>
+          <t>https://artportalen.se/Sighting/55545508</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55545587</v>
+        <v>55545129</v>
       </c>
       <c r="B15" t="n">
         <v>93233</v>
@@ -2140,14 +2156,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Eklund, SV om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697077</v>
+        <v>696785</v>
       </c>
       <c r="R15" t="n">
-        <v>6643814</v>
+        <v>6643600</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2182,11 +2198,6 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2211,13 +2222,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545587</t>
+          <t>https://artportalen.se/Sighting/55545129</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55545589</v>
+        <v>55545587</v>
       </c>
       <c r="B16" t="n">
         <v>93233</v>
@@ -2254,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697044</v>
+        <v>697077</v>
       </c>
       <c r="R16" t="n">
-        <v>6643821</v>
+        <v>6643814</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2321,13 +2332,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545589</t>
+          <t>https://artportalen.se/Sighting/55545587</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55545592</v>
+        <v>55545589</v>
       </c>
       <c r="B17" t="n">
         <v>93233</v>
@@ -2364,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697043</v>
+        <v>697044</v>
       </c>
       <c r="R17" t="n">
-        <v>6643847</v>
+        <v>6643821</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2431,13 +2442,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545592</t>
+          <t>https://artportalen.se/Sighting/55545589</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55545594</v>
+        <v>55545592</v>
       </c>
       <c r="B18" t="n">
         <v>93233</v>
@@ -2474,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697030</v>
+        <v>697043</v>
       </c>
       <c r="R18" t="n">
-        <v>6643834</v>
+        <v>6643847</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2541,13 +2552,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545594</t>
+          <t>https://artportalen.se/Sighting/55545592</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>55545704</v>
+        <v>55545594</v>
       </c>
       <c r="B19" t="n">
         <v>93233</v>
@@ -2584,10 +2595,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696975</v>
+        <v>697030</v>
       </c>
       <c r="R19" t="n">
-        <v>6643792</v>
+        <v>6643834</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2651,13 +2662,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545704</t>
+          <t>https://artportalen.se/Sighting/55545594</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55545706</v>
+        <v>55545704</v>
       </c>
       <c r="B20" t="n">
         <v>93233</v>
@@ -2694,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697163</v>
+        <v>696975</v>
       </c>
       <c r="R20" t="n">
-        <v>6643834</v>
+        <v>6643792</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2761,54 +2772,53 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545706</t>
+          <t>https://artportalen.se/Sighting/55545704</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>55545582</v>
+        <v>55545706</v>
       </c>
       <c r="B21" t="n">
-        <v>99096</v>
+        <v>93233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697087</v>
+        <v>697163</v>
       </c>
       <c r="R21" t="n">
-        <v>6643892</v>
+        <v>6643834</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2854,6 +2864,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2871,54 +2882,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545582</t>
+          <t>https://artportalen.se/Sighting/55545706</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>55545579</v>
+        <v>137373649</v>
       </c>
       <c r="B22" t="n">
-        <v>99141</v>
+        <v>93497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697113</v>
+        <v>697031</v>
       </c>
       <c r="R22" t="n">
-        <v>6643924</v>
+        <v>6643872</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2945,17 +2953,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2015-10-20</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2015-10-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,74 +2983,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545579</t>
+          <t>https://artportalen.se/Sighting/137373649</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132823493</v>
+        <v>137373650</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>93497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696964</v>
+        <v>697031</v>
       </c>
       <c r="R23" t="n">
-        <v>6643823</v>
+        <v>6643874</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3061,22 +3065,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,74 +3095,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132823493</t>
+          <t>https://artportalen.se/Sighting/137373650</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132824392</v>
+        <v>137373652</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>93497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697135</v>
+        <v>697073</v>
       </c>
       <c r="R24" t="n">
-        <v>6643852</v>
+        <v>6643889</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3182,22 +3177,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,27 +3207,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132824392</t>
+          <t>https://artportalen.se/Sighting/137373652</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55544918</v>
+        <v>55545582</v>
       </c>
       <c r="B25" t="n">
-        <v>101326</v>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,21 +3235,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3263,14 +3258,14 @@
       <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ekllund, SV om, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696728</v>
+        <v>697087</v>
       </c>
       <c r="R25" t="n">
-        <v>6643586</v>
+        <v>6643892</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3305,6 +3300,11 @@
           <t>2015-10-07</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3328,16 +3328,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55544918</t>
+          <t>https://artportalen.se/Sighting/55545582</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>55544981</v>
+        <v>137373653</v>
       </c>
       <c r="B26" t="n">
-        <v>101326</v>
+        <v>99388</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,37 +3345,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, SV om, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696765</v>
+        <v>697075</v>
       </c>
       <c r="R26" t="n">
-        <v>6643599</v>
+        <v>6643893</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3402,12 +3399,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,27 +3429,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55544981</t>
+          <t>https://artportalen.se/Sighting/137373653</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>55545580</v>
+        <v>55545579</v>
       </c>
       <c r="B27" t="n">
-        <v>101326</v>
+        <v>99141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,21 +3457,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3507,12 +3514,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3543,57 +3550,63 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545580</t>
+          <t>https://artportalen.se/Sighting/55545579</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>55545586</v>
+        <v>132823493</v>
       </c>
       <c r="B28" t="n">
-        <v>101326</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697078</v>
+        <v>696964</v>
       </c>
       <c r="R28" t="n">
-        <v>6643820</v>
+        <v>6643823</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3617,12 +3630,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,68 +3660,74 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545586</t>
+          <t>https://artportalen.se/Sighting/132823493</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>55545707</v>
+        <v>132824392</v>
       </c>
       <c r="B29" t="n">
-        <v>101326</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697163</v>
+        <v>697135</v>
       </c>
       <c r="R29" t="n">
-        <v>6643834</v>
+        <v>6643852</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3722,17 +3751,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3747,27 +3781,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545707</t>
+          <t>https://artportalen.se/Sighting/132824392</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132830921</v>
+        <v>55544918</v>
       </c>
       <c r="B30" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,19 +3827,22 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ekllund, SV om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697167</v>
+        <v>696728</v>
       </c>
       <c r="R30" t="n">
-        <v>6643826</v>
+        <v>6643586</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3829,22 +3866,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3859,27 +3886,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830921</t>
+          <t>https://artportalen.se/Sighting/55544918</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132830923</v>
+        <v>55544981</v>
       </c>
       <c r="B31" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,19 +3932,22 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, SV om, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697051</v>
+        <v>696765</v>
       </c>
       <c r="R31" t="n">
-        <v>6643938</v>
+        <v>6643599</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3941,22 +3971,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,27 +3991,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830923</t>
+          <t>https://artportalen.se/Sighting/55544981</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132830930</v>
+        <v>55545580</v>
       </c>
       <c r="B32" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4017,19 +4037,22 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697027</v>
+        <v>697113</v>
       </c>
       <c r="R32" t="n">
-        <v>6643874</v>
+        <v>6643924</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4053,22 +4076,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,49 +4101,49 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830930</t>
+          <t>https://artportalen.se/Sighting/55545580</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>55545583</v>
+        <v>55545586</v>
       </c>
       <c r="B33" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4138,10 +4156,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697082</v>
+        <v>697078</v>
       </c>
       <c r="R33" t="n">
-        <v>6643889</v>
+        <v>6643820</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4176,11 +4194,6 @@
           <t>2015-10-07</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>En frisk alm ca 70 år gammal. Gammal barrblandskog på delvis kalkhaltig mark.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4203,6 +4216,562 @@
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545586</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>55545707</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Eklund, NO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>697163</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6643834</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545707</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132830921</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>697167</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6643826</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830921</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132830923</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>697051</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6643938</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830923</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132830930</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fansjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>697027</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6643874</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830930</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>55545583</v>
+      </c>
+      <c r="B38" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Eklund, NO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>697082</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6643889</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>En frisk alm ca 70 år gammal. Gammal barrblandskog på delvis kalkhaltig mark.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/55545583</t>
         </is>
@@ -4242,6 +4811,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 6380-2022 artfynd.xlsx
+++ b/artfynd/S 6380-2022 artfynd.xlsx
@@ -2891,7 +2891,7 @@
         <v>137373649</v>
       </c>
       <c r="B22" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137373650</v>
       </c>
       <c r="B23" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>137373652</v>
       </c>
       <c r="B24" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137373653</v>
       </c>
       <c r="B26" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 6380-2022 artfynd.xlsx
+++ b/artfynd/S 6380-2022 artfynd.xlsx
@@ -1460,7 +1460,7 @@
         <v>137373651</v>
       </c>
       <c r="B9" t="n">
-        <v>90896</v>
+        <v>90901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>137373649</v>
       </c>
       <c r="B22" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137373650</v>
       </c>
       <c r="B23" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>137373652</v>
       </c>
       <c r="B24" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137373653</v>
       </c>
       <c r="B26" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 6380-2022 artfynd.xlsx
+++ b/artfynd/S 6380-2022 artfynd.xlsx
@@ -1460,7 +1460,7 @@
         <v>137373651</v>
       </c>
       <c r="B9" t="n">
-        <v>90901</v>
+        <v>90912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>137373649</v>
       </c>
       <c r="B22" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137373650</v>
       </c>
       <c r="B23" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>137373652</v>
       </c>
       <c r="B24" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137373653</v>
       </c>
       <c r="B26" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 6380-2022 artfynd.xlsx
+++ b/artfynd/S 6380-2022 artfynd.xlsx
@@ -1460,7 +1460,7 @@
         <v>137373651</v>
       </c>
       <c r="B9" t="n">
-        <v>90912</v>
+        <v>90913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>137373649</v>
       </c>
       <c r="B22" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137373650</v>
       </c>
       <c r="B23" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>137373652</v>
       </c>
       <c r="B24" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137373653</v>
       </c>
       <c r="B26" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 6380-2022 artfynd.xlsx
+++ b/artfynd/S 6380-2022 artfynd.xlsx
@@ -1460,7 +1460,7 @@
         <v>137373651</v>
       </c>
       <c r="B9" t="n">
-        <v>90913</v>
+        <v>90916</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>137373649</v>
       </c>
       <c r="B22" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137373650</v>
       </c>
       <c r="B23" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>137373652</v>
       </c>
       <c r="B24" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137373653</v>
       </c>
       <c r="B26" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 6380-2022 artfynd.xlsx
+++ b/artfynd/S 6380-2022 artfynd.xlsx
@@ -1460,7 +1460,7 @@
         <v>137373651</v>
       </c>
       <c r="B9" t="n">
-        <v>90916</v>
+        <v>90920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>137373649</v>
       </c>
       <c r="B22" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>137373650</v>
       </c>
       <c r="B23" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>137373652</v>
       </c>
       <c r="B24" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>137373653</v>
       </c>
       <c r="B26" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
